--- a/SchoolAPI/Reports/Generated/monthly-transactions-2026-04.xlsx
+++ b/SchoolAPI/Reports/Generated/monthly-transactions-2026-04.xlsx
@@ -20,7 +20,7 @@
     <t>Period: 2026-04-01 to 2026-04-30</t>
   </si>
   <si>
-    <t>Generated On: 2026-04-13 03:00:57 UTC</t>
+    <t>Generated On: 2026-05-01 00:44:29 UTC</t>
   </si>
   <si>
     <t>Date</t>
